--- a/tests/test_dataset/RepTest_correct.xlsx
+++ b/tests/test_dataset/RepTest_correct.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\Users\Main\Documents\Louis\Travail\IGDR\Repositories\Concatenate\PythonScript\tests\test_dataset\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\llenezet\Documents\Repositories\Files2DB\tests\test_dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ECA5CE9-AC06-4D1A-8F23-59AA279D3086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2318F0D-32EC-4681-9E97-0EB22AFAB774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6300" yWindow="3270" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Files" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="111">
   <si>
     <t>Eq</t>
   </si>
@@ -103,27 +103,6 @@
     <t>ToDate</t>
   </si>
   <si>
-    <t>Sep1Name</t>
-  </si>
-  <si>
-    <t>Sep1Pat</t>
-  </si>
-  <si>
-    <t>Sep2Name</t>
-  </si>
-  <si>
-    <t>Sep2Pat</t>
-  </si>
-  <si>
-    <t>Sep3Name</t>
-  </si>
-  <si>
-    <t>Sep3Pat</t>
-  </si>
-  <si>
-    <t>SepKeepLink</t>
-  </si>
-  <si>
     <t>Date</t>
   </si>
   <si>
@@ -172,39 +151,15 @@
     <t>Puce</t>
   </si>
   <si>
-    <t>(?P&lt;Data&gt;[0-9]*)</t>
-  </si>
-  <si>
     <t>Tatouage</t>
   </si>
   <si>
-    <t>(?P&lt;Data&gt;[A-Z0-9]+[A-Z][A-Z0-9]*)</t>
-  </si>
-  <si>
     <t>FCI</t>
   </si>
   <si>
     <t xml:space="preserve"> ou </t>
   </si>
   <si>
-    <t>G</t>
-  </si>
-  <si>
-    <t>(?P&lt;Data&gt;[A-E])(?P&lt;Other&gt;\/[A-E])</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>(?P&lt;Other&gt;[A-E]\/)(?P&lt;Data&gt;[A-E])</t>
-  </si>
-  <si>
-    <t>DG</t>
-  </si>
-  <si>
-    <t>(?P&lt;Data&gt;[A-E])</t>
-  </si>
-  <si>
     <t>Contains</t>
   </si>
   <si>
@@ -271,9 +226,6 @@
     <t>Dys</t>
   </si>
   <si>
-    <t>None</t>
-  </si>
-  <si>
     <t>EmplacementOrigine</t>
   </si>
   <si>
@@ -352,59 +304,77 @@
     <t>Mod</t>
   </si>
   <si>
+    <t>OlderFileName</t>
+  </si>
+  <si>
+    <t>FileName</t>
+  </si>
+  <si>
+    <t>Author</t>
+  </si>
+  <si>
+    <t>DateFileCreation</t>
+  </si>
+  <si>
+    <t>Somewhere</t>
+  </si>
+  <si>
+    <t>MySpecialFile</t>
+  </si>
+  <si>
+    <t>FileA</t>
+  </si>
+  <si>
+    <t>./PythonScript/tests/test_dataset/files/fileA.xlsx</t>
+  </si>
+  <si>
+    <t>Sheet1</t>
+  </si>
+  <si>
+    <t>Myself</t>
+  </si>
+  <si>
+    <t>SomewhereElse</t>
+  </si>
+  <si>
+    <t>FileB</t>
+  </si>
+  <si>
+    <t>./PythonScript/tests/test_dataset/files/fileB.csv</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>((?P&lt;G&gt;[A-E])(\/*)(?P&lt;D&gt;[A-E]))|(?P&lt;DG&gt;[A-E])</t>
+  </si>
+  <si>
+    <t>SepPattern</t>
+  </si>
+  <si>
+    <t>(?P&lt;Puce&gt;[0-9]{12,19})*(\s)*(?P&lt;Tatouage&gt;[A-Z0-9]+[A-Z][A-Z0-9]*)*</t>
+  </si>
+  <si>
     <t>OptColToNotUse</t>
   </si>
   <si>
-    <t>OlderFileName</t>
-  </si>
-  <si>
-    <t>FileName</t>
-  </si>
-  <si>
-    <t>Author</t>
-  </si>
-  <si>
-    <t>DateFileCreation</t>
-  </si>
-  <si>
-    <t>Somewhere</t>
-  </si>
-  <si>
-    <t>MySpecialFile</t>
-  </si>
-  <si>
-    <t>FileA</t>
-  </si>
-  <si>
-    <t>./PythonScript/tests/test_dataset/files/fileA.xlsx</t>
-  </si>
-  <si>
-    <t>Sheet1</t>
-  </si>
-  <si>
-    <t>Myself</t>
-  </si>
-  <si>
-    <t>SomewhereElse</t>
-  </si>
-  <si>
-    <t>FileB</t>
-  </si>
-  <si>
-    <t>./PythonScript/tests/test_dataset/files/fileB.csv</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>R</t>
+    <t>Dys_(\d+|NA)_</t>
+  </si>
+  <si>
+    <t>FCI,Date</t>
+  </si>
+  <si>
+    <t>DG,D,G</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -417,6 +387,12 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFA31515"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -668,8 +644,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1003,84 +979,84 @@
   <sheetData>
     <row r="1" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J1" t="s">
+        <v>69</v>
+      </c>
+      <c r="K1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M1" t="s">
+        <v>72</v>
+      </c>
+      <c r="N1" t="s">
         <v>79</v>
       </c>
-      <c r="B1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D1" t="s">
-        <v>96</v>
-      </c>
-      <c r="E1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F1" t="s">
-        <v>81</v>
-      </c>
-      <c r="G1" t="s">
-        <v>82</v>
-      </c>
-      <c r="H1" t="s">
-        <v>83</v>
-      </c>
-      <c r="I1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J1" t="s">
-        <v>85</v>
-      </c>
-      <c r="K1" t="s">
-        <v>108</v>
-      </c>
-      <c r="L1" t="s">
-        <v>86</v>
-      </c>
-      <c r="M1" t="s">
-        <v>88</v>
-      </c>
-      <c r="N1" t="s">
-        <v>95</v>
-      </c>
       <c r="O1" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="P1" s="22" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="Q1" s="22" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="R1" s="23" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="S1" s="24" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="T1" s="24" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="U1" s="24" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="D2" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="F2">
         <v>4</v>
@@ -1092,16 +1068,16 @@
         <v>3</v>
       </c>
       <c r="I2" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="J2" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="K2" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="L2" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="P2" s="18">
         <v>1</v>
@@ -1115,13 +1091,13 @@
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="C3" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="D3" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -1133,16 +1109,16 @@
         <v>1</v>
       </c>
       <c r="I3" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="J3" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="K3" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="L3" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -1169,13 +1145,13 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>15</v>
@@ -1190,51 +1166,51 @@
         <v>18</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="M1" s="15" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="N1" s="26" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="K2" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="M2" s="17"/>
     </row>
@@ -1243,18 +1219,18 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D3" s="6"/>
       <c r="H3" s="6"/>
       <c r="J3" s="7" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="K3" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="M3" s="17"/>
     </row>
@@ -1263,44 +1239,44 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D4" s="6"/>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="H4" s="6"/>
       <c r="J4" s="7" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="K4" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="M4" s="17"/>
     </row>
     <row r="5" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="F5" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="H5" s="6"/>
       <c r="J5" s="7"/>
       <c r="K5" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="L5" s="18">
         <v>111111</v>
@@ -1311,62 +1287,62 @@
     </row>
     <row r="6" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D6" s="6"/>
       <c r="H6" s="6"/>
       <c r="J6" s="7"/>
       <c r="K6" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="M6" s="17"/>
     </row>
     <row r="7" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="F7" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H7" s="6"/>
       <c r="J7" s="7" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="M7" s="17"/>
     </row>
     <row r="8" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D8" s="6"/>
       <c r="F8" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H8" s="6"/>
       <c r="J8" s="7"/>
       <c r="K8" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="L8" s="18">
         <v>111111111111111</v>
@@ -1377,24 +1353,24 @@
     </row>
     <row r="9" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D9" s="6"/>
       <c r="F9" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="H9" s="6"/>
       <c r="J9" s="7" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="K9" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="L9" s="18">
         <v>6</v>
@@ -1405,33 +1381,33 @@
     </row>
     <row r="10" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D10" s="6"/>
       <c r="H10" s="6"/>
       <c r="J10" s="7" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="K10" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="M10" s="17"/>
     </row>
     <row r="11" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="D11" s="11"/>
       <c r="E11" s="12"/>
@@ -1440,7 +1416,7 @@
       <c r="H11" s="11"/>
       <c r="I11" s="12"/>
       <c r="J11" s="13" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="K11" s="12"/>
       <c r="L11" s="20"/>
@@ -1456,21 +1432,22 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.5703125" customWidth="1"/>
-    <col min="5" max="10" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="69.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="19.42578125" bestFit="1" customWidth="1"/>
     <col min="14" max="16" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>15</v>
@@ -1482,10 +1459,10 @@
         <v>18</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>19</v>
@@ -1497,176 +1474,120 @@
         <v>21</v>
       </c>
       <c r="J1" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="K1" s="28" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="B2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="C2" t="s">
         <v>24</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q1" s="28" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" t="s">
-        <v>31</v>
       </c>
       <c r="D2" s="27"/>
       <c r="E2" s="6" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="H2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="I2" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="10"/>
-    </row>
-    <row r="3" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B3" s="6"/>
       <c r="D3" s="27"/>
       <c r="E3" s="6" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="H3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="I3" t="s">
-        <v>34</v>
-      </c>
-      <c r="P3" s="7"/>
-    </row>
-    <row r="4" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B4" s="6"/>
       <c r="D4" s="27"/>
       <c r="E4" s="6"/>
       <c r="H4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="P4" s="7"/>
-    </row>
-    <row r="5" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>41</v>
-      </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D5" s="27"/>
       <c r="E5" s="6"/>
       <c r="G5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H5" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="I5" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="J5" t="s">
-        <v>44</v>
-      </c>
-      <c r="K5" t="s">
-        <v>45</v>
-      </c>
-      <c r="L5" t="s">
-        <v>46</v>
-      </c>
-      <c r="M5" t="s">
-        <v>47</v>
-      </c>
-      <c r="P5" s="7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="C6" s="12"/>
       <c r="D6" s="12"/>
       <c r="E6" s="11"/>
       <c r="F6" s="12"/>
       <c r="G6" s="12" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="K6" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="L6" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="M6" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="N6" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="O6" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="P6" s="13" t="s">
-        <v>35</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -1680,35 +1601,46 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="B1" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="C1" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="D1" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="E1" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="F1" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>108</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -1729,7 +1661,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>

--- a/tests/test_dataset/RepTest_correct.xlsx
+++ b/tests/test_dataset/RepTest_correct.xlsx
@@ -1,23 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\llenezet\Documents\Repositories\Files2DB\tests\test_dataset\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\llenezet\repositories\Files2DB\tests\test_dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2318F0D-32EC-4681-9E97-0EB22AFAB774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A073AC-D8C8-455C-BA03-1416ECDD870C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Files" sheetId="1" r:id="rId1"/>
-    <sheet name="Fields" sheetId="2" r:id="rId2"/>
-    <sheet name="Formats" sheetId="3" r:id="rId3"/>
-    <sheet name="FieldsOrga" sheetId="5" r:id="rId4"/>
-    <sheet name="ValuesConv" sheetId="4" r:id="rId5"/>
+    <sheet name="FieldRules" sheetId="2" r:id="rId2"/>
+    <sheet name="ValuesMap" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="98">
   <si>
     <t>Eq</t>
   </si>
@@ -79,9 +77,6 @@
     <t>LabradorXGolden</t>
   </si>
   <si>
-    <t>Labxgol</t>
-  </si>
-  <si>
     <t>Sep</t>
   </si>
   <si>
@@ -94,24 +89,12 @@
     <t>DelEnd</t>
   </si>
   <si>
-    <t>Case</t>
-  </si>
-  <si>
-    <t>ToNum</t>
-  </si>
-  <si>
-    <t>ToDate</t>
-  </si>
-  <si>
     <t>Date</t>
   </si>
   <si>
     <t>et,+,\n</t>
   </si>
   <si>
-    <t>0,?,??,???,nan,00:00:00</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
@@ -124,24 +107,12 @@
     <t>T</t>
   </si>
   <si>
-    <t>String</t>
-  </si>
-  <si>
     <t>lower</t>
   </si>
   <si>
-    <t>Integer</t>
-  </si>
-  <si>
     <t>Int</t>
   </si>
   <si>
-    <t>PuceTatouage</t>
-  </si>
-  <si>
-    <t>/,\n</t>
-  </si>
-  <si>
     <t xml:space="preserve"> ,.</t>
   </si>
   <si>
@@ -154,12 +125,6 @@
     <t>Tatouage</t>
   </si>
   <si>
-    <t>FCI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ou </t>
-  </si>
-  <si>
     <t>Contains</t>
   </si>
   <si>
@@ -178,9 +143,6 @@
     <t xml:space="preserve"> dit , dite , = </t>
   </si>
   <si>
-    <t xml:space="preserve"> du cesecah,_2, 2,_3, 3, </t>
-  </si>
-  <si>
     <t>Title</t>
   </si>
   <si>
@@ -211,9 +173,6 @@
     <t>NumIdentification</t>
   </si>
   <si>
-    <t>\n,/</t>
-  </si>
-  <si>
     <t>ALPHANUM</t>
   </si>
   <si>
@@ -223,9 +182,6 @@
     <t>A,B,C,D,E</t>
   </si>
   <si>
-    <t>Dys</t>
-  </si>
-  <si>
     <t>EmplacementOrigine</t>
   </si>
   <si>
@@ -280,12 +236,6 @@
     <t>FilePath</t>
   </si>
   <si>
-    <t>StripEnd</t>
-  </si>
-  <si>
-    <t>StripStart</t>
-  </si>
-  <si>
     <t>Type</t>
   </si>
   <si>
@@ -295,15 +245,6 @@
     <t>Category</t>
   </si>
   <si>
-    <t>SepGive</t>
-  </si>
-  <si>
-    <t>ParentField</t>
-  </si>
-  <si>
-    <t>Mod</t>
-  </si>
-  <si>
     <t>OlderFileName</t>
   </si>
   <si>
@@ -355,26 +296,44 @@
     <t>SepPattern</t>
   </si>
   <si>
-    <t>(?P&lt;Puce&gt;[0-9]{12,19})*(\s)*(?P&lt;Tatouage&gt;[A-Z0-9]+[A-Z][A-Z0-9]*)*</t>
-  </si>
-  <si>
-    <t>OptColToNotUse</t>
-  </si>
-  <si>
-    <t>Dys_(\d+|NA)_</t>
-  </si>
-  <si>
-    <t>FCI,Date</t>
-  </si>
-  <si>
-    <t>DG,D,G</t>
+    <t>(?P&lt;Puce&gt;[0-9]{12,19})*(\s|\n|\/)*(?P&lt;Tatouage&gt;[A-Z0-9]+[A-Z][A-Z0-9]*)*</t>
+  </si>
+  <si>
+    <t>KeepLink</t>
+  </si>
+  <si>
+    <t>Dys_(NA|\d+)_FCI</t>
+  </si>
+  <si>
+    <t>Dys_(NA|\d+)_FCI_(G|D|DG)</t>
+  </si>
+  <si>
+    <t>LabxGol</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>DelStart</t>
+  </si>
+  <si>
+    <t>StripFrom</t>
+  </si>
+  <si>
+    <t>_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  du cesecah, \d+</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -388,12 +347,6 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFA31515"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -403,7 +356,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -477,7 +430,9 @@
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
-      <right/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
@@ -485,40 +440,24 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="medium">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </right>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
@@ -527,33 +466,7 @@
     <border>
       <left/>
       <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </right>
       <top/>
       <bottom/>
@@ -563,7 +476,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -577,31 +490,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -620,32 +509,31 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -963,15 +851,15 @@
     <col min="6" max="6" width="8.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8" style="25" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="7.140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8" style="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="7.140625" style="15" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.42578125" style="25" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.7109375" style="25" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.42578125" style="25" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.42578125" style="15" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.7109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.42578125" style="15" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="5.85546875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="12.7109375" bestFit="1" customWidth="1"/>
@@ -979,84 +867,84 @@
   <sheetData>
     <row r="1" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="B1" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="C1" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="D1" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E1" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="F1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L1" t="s">
+        <v>56</v>
+      </c>
+      <c r="M1" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1" t="s">
         <v>65</v>
       </c>
-      <c r="G1" t="s">
-        <v>66</v>
-      </c>
-      <c r="H1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I1" t="s">
-        <v>68</v>
-      </c>
-      <c r="J1" t="s">
-        <v>69</v>
-      </c>
-      <c r="K1" t="s">
-        <v>91</v>
-      </c>
-      <c r="L1" t="s">
-        <v>70</v>
-      </c>
-      <c r="M1" t="s">
-        <v>72</v>
-      </c>
-      <c r="N1" t="s">
-        <v>79</v>
-      </c>
       <c r="O1" t="s">
-        <v>92</v>
-      </c>
-      <c r="P1" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q1" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="R1" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="S1" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="T1" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="U1" s="24" t="s">
-        <v>75</v>
+      <c r="P1" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q1" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="R1" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="S1" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="T1" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="U1" s="14" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="E2" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="F2">
         <v>4</v>
@@ -1068,36 +956,36 @@
         <v>3</v>
       </c>
       <c r="I2" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="J2" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="K2" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="L2" t="s">
-        <v>78</v>
-      </c>
-      <c r="P2" s="18">
+        <v>64</v>
+      </c>
+      <c r="P2" s="10">
         <v>1</v>
       </c>
-      <c r="Q2" s="19">
+      <c r="Q2" s="11">
         <v>1</v>
       </c>
-      <c r="R2" s="18">
+      <c r="R2" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -1109,16 +997,16 @@
         <v>1</v>
       </c>
       <c r="I3" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="J3" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="K3" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="L3" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1131,296 +1019,342 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" customWidth="1"/>
-    <col min="8" max="11" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.140625" style="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.5703125" style="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="18.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="68.85546875" style="17" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.42578125" style="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="D1" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>16</v>
       </c>
       <c r="F1" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="I1" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="N1" s="18" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="L2" s="9"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="19"/>
+    </row>
+    <row r="3" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="16"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="L3" s="9"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="19"/>
+    </row>
+    <row r="4" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="16"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="17"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="L4" s="9"/>
+      <c r="M4" s="16"/>
+      <c r="N4" s="19"/>
+    </row>
+    <row r="5" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="17"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="J5" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="K5" s="10">
+        <v>111111</v>
+      </c>
+      <c r="L5" s="11">
+        <v>999999</v>
+      </c>
+      <c r="M5" s="16"/>
+      <c r="N5" s="19"/>
+    </row>
+    <row r="6" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="20"/>
+      <c r="I6" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="J6" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="L1" s="14" t="s">
+      <c r="L6" s="9"/>
+      <c r="N6" s="20"/>
+    </row>
+    <row r="7" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="N1" s="26" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="7" t="s">
+      <c r="C7" s="16"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="17"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" s="17"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="N7" s="20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="16"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="17"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="J8" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" s="10">
+        <v>111111111111111</v>
+      </c>
+      <c r="L8" s="11">
+        <v>999999999999999</v>
+      </c>
+      <c r="M8" s="16"/>
+      <c r="N8" s="19"/>
+    </row>
+    <row r="9" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="B9" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="16"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="17"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="H2" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I2" s="9" t="s">
+      <c r="K9" s="10">
+        <v>6</v>
+      </c>
+      <c r="L9" s="11">
+        <v>9</v>
+      </c>
+      <c r="M9" s="16"/>
+      <c r="N9" s="19"/>
+    </row>
+    <row r="10" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="J10" s="17"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="N10" s="19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="16"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="J11" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="K2" t="s">
-        <v>49</v>
-      </c>
-      <c r="M2" s="17"/>
-    </row>
-    <row r="3" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="J3" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" t="s">
-        <v>51</v>
-      </c>
-      <c r="M3" s="17"/>
-    </row>
-    <row r="4" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="6"/>
-      <c r="F4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="6"/>
-      <c r="J4" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="K4" t="s">
-        <v>52</v>
-      </c>
-      <c r="M4" s="17"/>
-    </row>
-    <row r="5" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="F5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="6"/>
-      <c r="J5" s="7"/>
-      <c r="K5" t="s">
-        <v>32</v>
-      </c>
-      <c r="L5" s="18">
-        <v>111111</v>
-      </c>
-      <c r="M5" s="19">
-        <v>999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="J6" s="7"/>
-      <c r="K6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M6" s="17"/>
-    </row>
-    <row r="7" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="F7" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" s="6"/>
-      <c r="J7" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="M7" s="17"/>
-    </row>
-    <row r="8" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="6"/>
-      <c r="F8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8" s="6"/>
-      <c r="J8" s="7"/>
-      <c r="K8" t="s">
-        <v>32</v>
-      </c>
-      <c r="L8" s="18">
-        <v>111111111111111</v>
-      </c>
-      <c r="M8" s="19">
-        <v>999999999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="6"/>
-      <c r="F9" t="s">
-        <v>25</v>
-      </c>
-      <c r="H9" s="6"/>
-      <c r="J9" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="K9" t="s">
-        <v>59</v>
-      </c>
-      <c r="L9" s="18">
-        <v>6</v>
-      </c>
-      <c r="M9" s="19">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" t="s">
-        <v>60</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="J10" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="K10" t="s">
-        <v>61</v>
-      </c>
-      <c r="M10" s="17"/>
-    </row>
-    <row r="11" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="K11" s="12"/>
-      <c r="L11" s="20"/>
-      <c r="M11" s="21"/>
+      <c r="L11" s="9"/>
+      <c r="N11" s="19"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1428,227 +1362,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="3" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" customWidth="1"/>
-    <col min="5" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="69.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="13.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="K1" s="28" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" s="27"/>
-      <c r="E2" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" s="9"/>
-    </row>
-    <row r="3" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="6"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="6"/>
-      <c r="H4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="27"/>
-      <c r="E5" s="6"/>
-      <c r="G5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J5" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>104</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -1656,12 +1369,14 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1731,7 +1446,7 @@
         <v>13</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>14</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/tests/test_dataset/RepTest_correct.xlsx
+++ b/tests/test_dataset/RepTest_correct.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\llenezet\repositories\Files2DB\tests\test_dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A073AC-D8C8-455C-BA03-1416ECDD870C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{308B374E-5D12-41D9-8A6C-63C089CC7EAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Files" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="99">
   <si>
     <t>Eq</t>
   </si>
@@ -327,6 +327,9 @@
   </si>
   <si>
     <t xml:space="preserve">  du cesecah, \d+</t>
+  </si>
+  <si>
+    <t>OptColToNotUse</t>
   </si>
 </sst>
 </file>
@@ -476,7 +479,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -532,9 +535,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1019,7 +1019,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.140625" bestFit="1" customWidth="1"/>
@@ -1031,9 +1031,10 @@
     <col min="11" max="12" width="18.42578125" style="8" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="68.85546875" style="17" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="9.42578125" style="17" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>68</v>
       </c>
@@ -1076,8 +1077,11 @@
       <c r="N1" s="18" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>33</v>
       </c>
@@ -1106,7 +1110,7 @@
       <c r="M2" s="16"/>
       <c r="N2" s="19"/>
     </row>
-    <row r="3" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
@@ -1129,7 +1133,7 @@
       <c r="M3" s="16"/>
       <c r="N3" s="19"/>
     </row>
-    <row r="4" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>8</v>
       </c>
@@ -1154,7 +1158,7 @@
       <c r="M4" s="16"/>
       <c r="N4" s="19"/>
     </row>
-    <row r="5" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>41</v>
       </c>
@@ -1186,7 +1190,7 @@
       <c r="M5" s="16"/>
       <c r="N5" s="19"/>
     </row>
-    <row r="6" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>44</v>
       </c>
@@ -1212,7 +1216,7 @@
       <c r="L6" s="9"/>
       <c r="N6" s="20"/>
     </row>
-    <row r="7" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>45</v>
       </c>
@@ -1239,7 +1243,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>28</v>
       </c>
@@ -1269,7 +1273,7 @@
       <c r="M8" s="16"/>
       <c r="N8" s="19"/>
     </row>
-    <row r="9" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>29</v>
       </c>
@@ -1299,7 +1303,7 @@
       <c r="M9" s="16"/>
       <c r="N9" s="19"/>
     </row>
-    <row r="10" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>89</v>
       </c>
@@ -1324,8 +1328,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
         <v>90</v>
       </c>
       <c r="B11" s="20" t="s">
@@ -1346,7 +1350,7 @@
       <c r="L11" s="9"/>
       <c r="N11" s="19"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
       <c r="D12" s="17"/>

--- a/tests/test_dataset/RepTest_correct.xlsx
+++ b/tests/test_dataset/RepTest_correct.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\llenezet\repositories\Files2DB\tests\test_dataset\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\llenezet\Documents\Repositories\Files2DB\tests\test_dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{308B374E-5D12-41D9-8A6C-63C089CC7EAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AB8B1B5-5FCD-42FF-8B99-EF5A7D2A82E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="100">
   <si>
     <t>Eq</t>
   </si>
@@ -80,9 +80,6 @@
     <t>Sep</t>
   </si>
   <si>
-    <t>Del</t>
-  </si>
-  <si>
     <t>DelIn</t>
   </si>
   <si>
@@ -236,9 +233,6 @@
     <t>FilePath</t>
   </si>
   <si>
-    <t>Type</t>
-  </si>
-  <si>
     <t>Field</t>
   </si>
   <si>
@@ -330,6 +324,15 @@
   </si>
   <si>
     <t>OptColToNotUse</t>
+  </si>
+  <si>
+    <t>Separator</t>
+  </si>
+  <si>
+    <t>DataType</t>
+  </si>
+  <si>
+    <t>DelMatch</t>
   </si>
 </sst>
 </file>
@@ -479,7 +482,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -535,6 +538,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -840,7 +846,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:V3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
@@ -865,86 +871,89 @@
     <col min="21" max="21" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" t="s">
         <v>49</v>
       </c>
-      <c r="B1" t="s">
+      <c r="F1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K1" t="s">
         <v>70</v>
       </c>
-      <c r="C1" t="s">
+      <c r="L1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N1" t="s">
+        <v>64</v>
+      </c>
+      <c r="O1" t="s">
         <v>71</v>
       </c>
-      <c r="D1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I1" t="s">
-        <v>54</v>
-      </c>
-      <c r="J1" t="s">
-        <v>55</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="P1" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q1" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="R1" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="S1" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="T1" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="U1" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="V1" s="21" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>72</v>
       </c>
-      <c r="L1" t="s">
-        <v>56</v>
-      </c>
-      <c r="M1" t="s">
-        <v>58</v>
-      </c>
-      <c r="N1" t="s">
-        <v>65</v>
-      </c>
-      <c r="O1" t="s">
+      <c r="B2" t="s">
         <v>73</v>
       </c>
-      <c r="P1" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q1" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="R1" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="S1" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="T1" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="U1" s="14" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="C2" t="s">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>75</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>76</v>
-      </c>
-      <c r="D2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E2" t="s">
-        <v>78</v>
       </c>
       <c r="F2">
         <v>4</v>
@@ -956,16 +965,16 @@
         <v>3</v>
       </c>
       <c r="I2" t="s">
+        <v>61</v>
+      </c>
+      <c r="J2" t="s">
         <v>62</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L2" t="s">
         <v>63</v>
-      </c>
-      <c r="K2" t="s">
-        <v>79</v>
-      </c>
-      <c r="L2" t="s">
-        <v>64</v>
       </c>
       <c r="P2" s="10">
         <v>1</v>
@@ -977,15 +986,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" t="s">
         <v>80</v>
-      </c>
-      <c r="C3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D3" t="s">
-        <v>82</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -997,16 +1006,16 @@
         <v>1</v>
       </c>
       <c r="I3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1036,75 +1045,75 @@
   <sheetData>
     <row r="1" spans="1:15" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="H1" s="18" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I1" s="18" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="J1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="L1" s="7" t="s">
-        <v>32</v>
-      </c>
       <c r="M1" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="N1" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="N1" s="18" t="s">
-        <v>88</v>
-      </c>
       <c r="O1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="C2" s="16" t="s">
         <v>34</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>35</v>
       </c>
       <c r="D2" s="17"/>
       <c r="E2" s="17"/>
       <c r="F2" s="17"/>
       <c r="G2" s="16" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H2" s="19" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I2" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="J2" s="17" t="s">
         <v>36</v>
-      </c>
-      <c r="J2" s="17" t="s">
-        <v>37</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="16"/>
@@ -1115,7 +1124,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C3" s="16"/>
       <c r="D3" s="17"/>
@@ -1124,10 +1133,10 @@
       <c r="G3" s="16"/>
       <c r="H3" s="20"/>
       <c r="I3" s="19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J3" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L3" s="9"/>
       <c r="M3" s="16"/>
@@ -1138,21 +1147,21 @@
         <v>8</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C4" s="16"/>
       <c r="D4" s="17"/>
       <c r="E4" s="17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F4" s="17"/>
       <c r="G4" s="16"/>
       <c r="H4" s="20"/>
       <c r="I4" s="19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L4" s="9"/>
       <c r="M4" s="16"/>
@@ -1160,26 +1169,26 @@
     </row>
     <row r="5" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="C5" s="16" t="s">
         <v>42</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>43</v>
       </c>
       <c r="D5" s="17"/>
       <c r="E5" s="17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F5" s="17"/>
       <c r="G5" s="16"/>
       <c r="H5" s="20"/>
       <c r="I5" s="19" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J5" s="17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K5" s="10">
         <v>111111</v>
@@ -1192,77 +1201,77 @@
     </row>
     <row r="6" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
       <c r="F6" s="17"/>
       <c r="G6" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H6" s="20"/>
       <c r="I6" s="19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J6" s="17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L6" s="9"/>
       <c r="N6" s="20"/>
     </row>
     <row r="7" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C7" s="16"/>
       <c r="D7" s="17"/>
       <c r="E7" s="17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F7" s="17"/>
       <c r="G7" s="16"/>
       <c r="H7" s="20"/>
       <c r="I7" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J7" s="17"/>
       <c r="L7" s="9"/>
       <c r="M7" s="17" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="N7" s="20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C8" s="16"/>
       <c r="D8" s="17"/>
       <c r="E8" s="17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F8" s="17"/>
       <c r="G8" s="16"/>
       <c r="H8" s="20"/>
       <c r="I8" s="19" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J8" s="17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K8" s="10">
         <v>111111111111111</v>
@@ -1275,24 +1284,24 @@
     </row>
     <row r="9" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C9" s="16"/>
       <c r="D9" s="17"/>
       <c r="E9" s="17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F9" s="17"/>
       <c r="G9" s="16"/>
       <c r="H9" s="20"/>
       <c r="I9" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J9" s="17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K9" s="10">
         <v>6</v>
@@ -1305,10 +1314,10 @@
     </row>
     <row r="10" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C10" s="16"/>
       <c r="D10" s="17"/>
@@ -1317,23 +1326,23 @@
       <c r="G10" s="16"/>
       <c r="H10" s="20"/>
       <c r="I10" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J10" s="17"/>
       <c r="L10" s="9"/>
       <c r="M10" s="16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N10" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" s="16"/>
       <c r="D11" s="17"/>
@@ -1342,10 +1351,10 @@
       <c r="G11" s="16"/>
       <c r="H11" s="20"/>
       <c r="I11" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J11" s="17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L11" s="9"/>
       <c r="N11" s="19"/>
@@ -1380,7 +1389,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1450,7 +1459,7 @@
         <v>13</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
